--- a/public/filesExcel/templateAidDistribution.xlsx
+++ b/public/filesExcel/templateAidDistribution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alsaeyd Alakhras\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02-Programming\01-Working-Companies\02-Salah\Projects\aid-registry\public\filesExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C5BB53-051B-4A1F-A809-32D7257DC389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DD8E01-C8BD-4E30-8A10-2AE07EF30E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{968E9332-7B49-4115-A4F6-A335BA14C462}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="قاعدة البيانات" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">المساعدات!$B$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">المساعدات!$B$1:$K$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">المساعدات!$1:$1</definedName>
     <definedName name="بيانات_المعيل">#REF!</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>رقم الهوية</t>
   </si>
@@ -160,6 +160,15 @@
   </si>
   <si>
     <t>رقم المشروع</t>
+  </si>
+  <si>
+    <t>الكفالات</t>
+  </si>
+  <si>
+    <t>المشاريع</t>
+  </si>
+  <si>
+    <t>المقر العام</t>
   </si>
 </sst>
 </file>
@@ -282,7 +291,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -302,9 +311,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -655,104 +661,104 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.6640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.44140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.77734375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.6640625" style="10" customWidth="1"/>
-    <col min="17" max="17" width="23.77734375" style="10" customWidth="1"/>
-    <col min="18" max="18" width="15.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.21875" style="10" customWidth="1"/>
-    <col min="22" max="22" width="17.109375" style="4" customWidth="1"/>
-    <col min="23" max="23" width="43.5546875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="17.109375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="43.5546875" style="9" customWidth="1"/>
+    <col min="15" max="15" width="16" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.6640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.44140625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="31.6640625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="3" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:23" s="3" customFormat="1" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:T1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="B1:K1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.17" top="0.4" bottom="0.25" header="0.31496062992125984" footer="0.18"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -763,19 +769,19 @@
           <x14:formula1>
             <xm:f>'قاعدة البيانات'!$E$5:$E$9</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>O2:O1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2CAA6455-0F69-4AFA-AD8D-B12E655A1319}">
           <x14:formula1>
-            <xm:f>'قاعدة البيانات'!$G$5:$G$15</xm:f>
+            <xm:f>'قاعدة البيانات'!$G$5:$G$16</xm:f>
           </x14:formula1>
-          <xm:sqref>Q2:Q1048576</xm:sqref>
+          <xm:sqref>H2:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{21F83EC2-A682-4B1D-BACD-990766473C14}">
           <x14:formula1>
             <xm:f>'قاعدة البيانات'!$I$5:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>R2:R1048576</xm:sqref>
+          <xm:sqref>I2:I1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -785,25 +791,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB86C78-D508-4A13-BCB3-B72A50FA9E65}">
-  <dimension ref="E2:L13"/>
+  <dimension ref="E2:L16"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="5:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
     </row>
     <row r="4" spans="5:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="E4" s="5" t="s">
@@ -880,6 +886,21 @@
     <row r="13" spans="5:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="G13" s="6" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="G14" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="5:12" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="G15" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="5:12" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="G16" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
